--- a/engine/tmgh_study/TMGH_Valuation_Model_02092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_02092026.xlsx
@@ -2040,10 +2040,10 @@
         <v>0.2437485685188716</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>196.5101788932792</v>
+        <v>271.0097219359063</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>125.5209481014641</v>
+        <v>201.9928263791846</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -2055,10 +2055,10 @@
         <v>0.2837485685188716</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>149.4396952483696</v>
+        <v>176.7313597873591</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>84.40789729584293</v>
+        <v>110.4074870648236</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -2070,10 +2070,10 @@
         <v>0.3037485685188716</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>134.6689258121608</v>
+        <v>154.2485079051968</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>73.17595754356496</v>
+        <v>90.66811154375614</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -2085,10 +2085,10 @@
         <v>0.3237485685188716</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>123.028438127374</v>
+        <v>137.8335452189615</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>65.16331605181323</v>
+        <v>77.41930420141432</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -2100,10 +2100,10 @@
         <v>0.3437485685188716</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>113.5921213965149</v>
+        <v>125.1868997487276</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>59.32000632749752</v>
+        <v>68.13130542984428</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -2115,10 +2115,10 @@
         <v>0.3637485685188716</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>105.782092460582</v>
+        <v>115.0940800067925</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>54.98967616003811</v>
+        <v>61.43676650619747</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -2130,10 +2130,10 @@
         <v>0.4037485685188716</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>93.61726151188044</v>
+        <v>99.95118102122261</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>49.27647548446123</v>
+        <v>52.84941767349388</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -2157,7 +2157,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>58.53797697850982</v>
+        <v>70.40402547889197</v>
       </c>
     </row>
     <row r="12">
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>84.50337145192553</v>
+        <v>97.01157757666864</v>
       </c>
     </row>
     <row r="13">
@@ -2173,7 +2173,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>103.6680228307067</v>
+        <v>116.8972107007202</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>118.4978488759164</v>
+        <v>132.4633469532804</v>
       </c>
     </row>
     <row r="15">
@@ -2189,7 +2189,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>130.3555583231125</v>
+        <v>145.0401671473733</v>
       </c>
     </row>
     <row r="16">
@@ -2197,7 +2197,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>148.1768744855158</v>
+        <v>164.1901212305032</v>
       </c>
     </row>
   </sheetData>
@@ -2660,17 +2660,17 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>221705.727430978</v>
+        <v>258122.7066734643</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>244183.0425779828</v>
+        <v>272961.0992599957</v>
       </c>
       <c r="D7" s="9">
         <f>C7/$B$3</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n">
-        <v>113.2392192375924</v>
+        <v>130.9117556153606</v>
       </c>
       <c r="F7" s="10">
         <f>D7/$B$2-1</f>
@@ -2684,17 +2684,17 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>78802.21433028321</v>
+        <v>108986.3993310054</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>131255.351000734</v>
+        <v>155108.0209618311</v>
       </c>
       <c r="D8" s="9">
         <f>C8/$B$3</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n">
-        <v>43.89059158325536</v>
+        <v>58.53845965343884</v>
       </c>
       <c r="F8" s="10">
         <f>D8/$B$2-1</f>
@@ -2708,17 +2708,17 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>233519.8692404983</v>
+        <v>272126.2458015337</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>253519.0185352381</v>
+        <v>284027.2187229249</v>
       </c>
       <c r="D9" s="9">
         <f>C9/$B$3</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n">
-        <v>118.9724199380305</v>
+        <v>137.7074333405901</v>
       </c>
       <c r="F9" s="10">
         <f>D9/$B$2-1</f>
@@ -2732,17 +2732,17 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>82628.51271199735</v>
+        <v>114587.7069754378</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>134279.0348427699</v>
+        <v>159534.3833960004</v>
       </c>
       <c r="D10" s="9">
         <f>C10/$B$3</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n">
-        <v>45.74742866171763</v>
+        <v>61.25667832968244</v>
       </c>
       <c r="F10" s="10">
         <f>D10/$B$2-1</f>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>0.2193244111908764</v>
+        <v>0.187048144397903</v>
       </c>
     </row>
   </sheetData>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>43.89059158325536</v>
+        <v>58.53845965343884</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>118.9724199380305</v>
+        <v>137.7074333405901</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>183703.1858848733</v>
+        <v>200776.4099615372</v>
       </c>
     </row>
     <row r="3">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>14029.00760827959</v>
+        <v>19657.36059272634</v>
       </c>
     </row>
     <row r="4">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>23973.53393782507</v>
+        <v>37688.93611920074</v>
       </c>
     </row>
     <row r="5">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-64816.58485299512</v>
+        <v>-72455.5074134685</v>
       </c>
     </row>
     <row r="13">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>14029.00760827959</v>
+        <v>19657.36059272634</v>
       </c>
     </row>
     <row r="14">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>23973.53393782507</v>
+        <v>37688.93611920074</v>
       </c>
     </row>
     <row r="15">
